--- a/songs/AllTheThingsSheSaid_v1/quelle/struktur-raster.xlsx
+++ b/songs/AllTheThingsSheSaid_v1/quelle/struktur-raster.xlsx
@@ -2823,7 +2823,7 @@
     </row>
     <row r="6" collapsed="1" ht="28.8" customHeight="1">
       <c r="A6" s="37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="7" hidden="1" outlineLevel="2">
       <c r="A7" s="37" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="C7" s="41" t="n"/>
       <c r="D7" s="41" t="n"/>
@@ -2861,7 +2861,7 @@
     </row>
     <row r="8" hidden="1" outlineLevel="2">
       <c r="A8" s="37" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="C8" s="41" t="n"/>
       <c r="D8" s="41" t="n"/>
@@ -2870,7 +2870,7 @@
     </row>
     <row r="9" hidden="1" outlineLevel="2">
       <c r="A9" s="37" t="n">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="C9" s="41" t="n"/>
       <c r="D9" s="41" t="n"/>
@@ -2879,7 +2879,7 @@
     </row>
     <row r="10" collapsed="1" ht="57.6" customHeight="1">
       <c r="A10" s="38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
     </row>
     <row r="11" hidden="1" outlineLevel="2">
       <c r="A11" s="38" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="C11" s="41" t="n"/>
       <c r="D11" s="41" t="n"/>
@@ -2913,7 +2913,7 @@
     </row>
     <row r="12" hidden="1" outlineLevel="2">
       <c r="A12" s="38" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="C12" s="41" t="n"/>
       <c r="D12" s="41" t="n"/>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="13" hidden="1" outlineLevel="2">
       <c r="A13" s="38" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="C13" s="41" t="n"/>
       <c r="D13" s="41" t="n"/>
@@ -2931,7 +2931,7 @@
     </row>
     <row r="14" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A14" s="38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="41" t="n"/>
       <c r="D14" s="41" t="n"/>
@@ -2940,7 +2940,7 @@
     </row>
     <row r="15" hidden="1" outlineLevel="2">
       <c r="A15" s="38" t="n">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="C15" s="41" t="n"/>
       <c r="D15" s="41" t="n"/>
@@ -2949,7 +2949,7 @@
     </row>
     <row r="16" hidden="1" outlineLevel="2">
       <c r="A16" s="38" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="C16" s="41" t="n"/>
       <c r="D16" s="41" t="n"/>
@@ -2958,7 +2958,7 @@
     </row>
     <row r="17" hidden="1" outlineLevel="2">
       <c r="A17" s="38" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="C17" s="41" t="n"/>
       <c r="D17" s="41" t="n"/>
@@ -2967,7 +2967,7 @@
     </row>
     <row r="18" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A18" s="38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" s="41" t="n"/>
       <c r="D18" s="41" t="n"/>
@@ -2976,7 +2976,7 @@
     </row>
     <row r="19" hidden="1" outlineLevel="2">
       <c r="A19" s="38" t="n">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="C19" s="41" t="n"/>
       <c r="D19" s="41" t="n"/>
@@ -2985,7 +2985,7 @@
     </row>
     <row r="20" hidden="1" outlineLevel="2">
       <c r="A20" s="38" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="C20" s="41" t="n"/>
       <c r="D20" s="41" t="n"/>
@@ -2994,7 +2994,7 @@
     </row>
     <row r="21" hidden="1" outlineLevel="2">
       <c r="A21" s="38" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="C21" s="41" t="n"/>
       <c r="D21" s="41" t="n"/>
@@ -3003,7 +3003,7 @@
     </row>
     <row r="22" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A22" s="38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" s="41" t="n"/>
       <c r="D22" s="41" t="n"/>
@@ -3012,7 +3012,7 @@
     </row>
     <row r="23" hidden="1" outlineLevel="2">
       <c r="A23" s="38" t="n">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="C23" s="41" t="n"/>
       <c r="D23" s="41" t="n"/>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="24" hidden="1" outlineLevel="2">
       <c r="A24" s="38" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="C24" s="41" t="n"/>
       <c r="D24" s="41" t="n"/>
@@ -3030,7 +3030,7 @@
     </row>
     <row r="25" hidden="1" outlineLevel="2">
       <c r="A25" s="38" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="C25" s="41" t="n"/>
       <c r="D25" s="41" t="n"/>
@@ -3039,7 +3039,7 @@
     </row>
     <row r="26" collapsed="1" ht="43.2" customHeight="1">
       <c r="A26" s="38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
     </row>
     <row r="27" hidden="1" outlineLevel="2">
       <c r="A27" s="38" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="C27" s="41" t="n"/>
       <c r="D27" s="41" t="n"/>
@@ -3072,7 +3072,7 @@
     </row>
     <row r="28" hidden="1" outlineLevel="2">
       <c r="A28" s="38" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="C28" s="41" t="n"/>
       <c r="D28" s="41" t="n"/>
@@ -3081,7 +3081,7 @@
     </row>
     <row r="29" hidden="1" outlineLevel="2">
       <c r="A29" s="38" t="n">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="C29" s="41" t="n"/>
       <c r="D29" s="41" t="n"/>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="30" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A30" s="38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C30" s="41" t="n"/>
       <c r="D30" s="41" t="n"/>
@@ -3099,7 +3099,7 @@
     </row>
     <row r="31" hidden="1" outlineLevel="2">
       <c r="A31" s="38" t="n">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
       <c r="C31" s="41" t="n"/>
       <c r="D31" s="41" t="n"/>
@@ -3108,7 +3108,7 @@
     </row>
     <row r="32" hidden="1" outlineLevel="2">
       <c r="A32" s="38" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="C32" s="41" t="n"/>
       <c r="D32" s="41" t="n"/>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="33" hidden="1" outlineLevel="2">
       <c r="A33" s="38" t="n">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
       <c r="C33" s="41" t="n"/>
       <c r="D33" s="41" t="n"/>
@@ -3126,7 +3126,7 @@
     </row>
     <row r="34" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A34" s="38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C34" s="41" t="n"/>
       <c r="D34" s="41" t="n"/>
@@ -3135,7 +3135,7 @@
     </row>
     <row r="35" hidden="1" outlineLevel="2">
       <c r="A35" s="38" t="n">
-        <v>7.25</v>
+        <v>8.25</v>
       </c>
       <c r="C35" s="41" t="n"/>
       <c r="D35" s="41" t="n"/>
@@ -3144,7 +3144,7 @@
     </row>
     <row r="36" hidden="1" outlineLevel="2">
       <c r="A36" s="38" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="C36" s="41" t="n"/>
       <c r="D36" s="41" t="n"/>
@@ -3153,7 +3153,7 @@
     </row>
     <row r="37" hidden="1" outlineLevel="2">
       <c r="A37" s="38" t="n">
-        <v>7.75</v>
+        <v>8.75</v>
       </c>
       <c r="C37" s="41" t="n"/>
       <c r="D37" s="41" t="n"/>
@@ -3162,7 +3162,7 @@
     </row>
     <row r="38" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A38" s="38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C38" s="41" t="n"/>
       <c r="D38" s="41" t="n"/>
@@ -3171,7 +3171,7 @@
     </row>
     <row r="39" hidden="1" outlineLevel="2">
       <c r="A39" s="38" t="n">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
       <c r="C39" s="41" t="n"/>
       <c r="D39" s="41" t="n"/>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="40" hidden="1" outlineLevel="2">
       <c r="A40" s="38" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="C40" s="41" t="n"/>
       <c r="D40" s="41" t="n"/>
@@ -3189,7 +3189,7 @@
     </row>
     <row r="41" hidden="1" outlineLevel="2">
       <c r="A41" s="38" t="n">
-        <v>8.75</v>
+        <v>9.75</v>
       </c>
       <c r="C41" s="41" t="n"/>
       <c r="D41" s="41" t="n"/>
@@ -3198,7 +3198,7 @@
     </row>
     <row r="42" collapsed="1" ht="158.4" customHeight="1">
       <c r="A42" s="38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B42" s="19" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
     </row>
     <row r="43" hidden="1" outlineLevel="2">
       <c r="A43" s="38" t="n">
-        <v>9.25</v>
+        <v>10.25</v>
       </c>
       <c r="B43" s="19" t="n"/>
       <c r="C43" s="41" t="n"/>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="44" hidden="1" outlineLevel="2">
       <c r="A44" s="38" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="B44" s="19" t="n"/>
       <c r="C44" s="41" t="n"/>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="45" hidden="1" outlineLevel="2">
       <c r="A45" s="38" t="n">
-        <v>9.75</v>
+        <v>10.75</v>
       </c>
       <c r="B45" s="19" t="n"/>
       <c r="C45" s="41" t="n"/>
@@ -3254,7 +3254,7 @@
     </row>
     <row r="46" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A46" s="38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B46" s="19" t="n"/>
       <c r="C46" s="41" t="n"/>
@@ -3264,7 +3264,7 @@
     </row>
     <row r="47" hidden="1" outlineLevel="2">
       <c r="A47" s="38" t="n">
-        <v>10.25</v>
+        <v>11.25</v>
       </c>
       <c r="B47" s="19" t="n"/>
       <c r="C47" s="41" t="n"/>
@@ -3274,7 +3274,7 @@
     </row>
     <row r="48" hidden="1" outlineLevel="2">
       <c r="A48" s="38" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="B48" s="19" t="n"/>
       <c r="C48" s="41" t="n"/>
@@ -3284,7 +3284,7 @@
     </row>
     <row r="49" hidden="1" outlineLevel="2">
       <c r="A49" s="38" t="n">
-        <v>10.75</v>
+        <v>11.75</v>
       </c>
       <c r="B49" s="19" t="n"/>
       <c r="C49" s="41" t="n"/>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="50" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A50" s="38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B50" s="19" t="n"/>
       <c r="C50" s="41" t="n"/>
@@ -3304,7 +3304,7 @@
     </row>
     <row r="51" hidden="1" outlineLevel="2">
       <c r="A51" s="38" t="n">
-        <v>11.25</v>
+        <v>12.25</v>
       </c>
       <c r="B51" s="19" t="n"/>
       <c r="C51" s="41" t="n"/>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="52" hidden="1" outlineLevel="2">
       <c r="A52" s="38" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="B52" s="19" t="n"/>
       <c r="C52" s="41" t="n"/>
@@ -3324,7 +3324,7 @@
     </row>
     <row r="53" hidden="1" outlineLevel="2">
       <c r="A53" s="38" t="n">
-        <v>11.75</v>
+        <v>12.75</v>
       </c>
       <c r="B53" s="19" t="n"/>
       <c r="C53" s="41" t="n"/>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="54" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A54" s="38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B54" s="19" t="n"/>
       <c r="C54" s="41" t="n"/>
@@ -3344,7 +3344,7 @@
     </row>
     <row r="55" hidden="1" outlineLevel="2">
       <c r="A55" s="38" t="n">
-        <v>12.25</v>
+        <v>13.25</v>
       </c>
       <c r="B55" s="19" t="n"/>
       <c r="C55" s="41" t="n"/>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="56" hidden="1" outlineLevel="2">
       <c r="A56" s="38" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="B56" s="19" t="n"/>
       <c r="C56" s="41" t="n"/>
@@ -3364,7 +3364,7 @@
     </row>
     <row r="57" hidden="1" outlineLevel="2">
       <c r="A57" s="38" t="n">
-        <v>12.75</v>
+        <v>13.75</v>
       </c>
       <c r="B57" s="19" t="n"/>
       <c r="C57" s="41" t="n"/>
@@ -3374,7 +3374,7 @@
     </row>
     <row r="58" collapsed="1" ht="86.40000000000001" customHeight="1">
       <c r="A58" s="38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B58" s="19" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
     </row>
     <row r="59" hidden="1" outlineLevel="2">
       <c r="A59" s="38" t="n">
-        <v>13.25</v>
+        <v>14.25</v>
       </c>
       <c r="B59" s="19" t="n"/>
       <c r="C59" s="41" t="n"/>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="60" hidden="1" outlineLevel="2">
       <c r="A60" s="38" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="B60" s="19" t="n"/>
       <c r="C60" s="41" t="n"/>
@@ -3419,7 +3419,7 @@
     </row>
     <row r="61" hidden="1" outlineLevel="2">
       <c r="A61" s="38" t="n">
-        <v>13.75</v>
+        <v>14.75</v>
       </c>
       <c r="B61" s="19" t="n"/>
       <c r="C61" s="41" t="n"/>
@@ -3429,7 +3429,7 @@
     </row>
     <row r="62" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A62" s="38" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B62" s="19" t="n"/>
       <c r="C62" s="41" t="n"/>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="63" hidden="1" outlineLevel="2">
       <c r="A63" s="38" t="n">
-        <v>14.25</v>
+        <v>15.25</v>
       </c>
       <c r="B63" s="19" t="n"/>
       <c r="C63" s="41" t="n"/>
@@ -3449,7 +3449,7 @@
     </row>
     <row r="64" hidden="1" outlineLevel="2">
       <c r="A64" s="38" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="B64" s="19" t="n"/>
       <c r="C64" s="41" t="n"/>
@@ -3459,7 +3459,7 @@
     </row>
     <row r="65" hidden="1" outlineLevel="2">
       <c r="A65" s="38" t="n">
-        <v>14.75</v>
+        <v>15.75</v>
       </c>
       <c r="B65" s="19" t="n"/>
       <c r="C65" s="41" t="n"/>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="66" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A66" s="38" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B66" s="19" t="n"/>
       <c r="C66" s="41" t="n"/>
@@ -3479,7 +3479,7 @@
     </row>
     <row r="67" hidden="1" outlineLevel="2">
       <c r="A67" s="38" t="n">
-        <v>15.25</v>
+        <v>16.25</v>
       </c>
       <c r="B67" s="19" t="n"/>
       <c r="C67" s="41" t="n"/>
@@ -3489,7 +3489,7 @@
     </row>
     <row r="68" hidden="1" outlineLevel="2">
       <c r="A68" s="38" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="B68" s="19" t="n"/>
       <c r="C68" s="41" t="n"/>
@@ -3499,7 +3499,7 @@
     </row>
     <row r="69" hidden="1" outlineLevel="2">
       <c r="A69" s="38" t="n">
-        <v>15.75</v>
+        <v>16.75</v>
       </c>
       <c r="B69" s="19" t="n"/>
       <c r="C69" s="41" t="n"/>
@@ -3509,7 +3509,7 @@
     </row>
     <row r="70" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A70" s="38" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B70" s="19" t="n"/>
       <c r="C70" s="41" t="n"/>
@@ -3519,7 +3519,7 @@
     </row>
     <row r="71" hidden="1" outlineLevel="2">
       <c r="A71" s="38" t="n">
-        <v>16.25</v>
+        <v>17.25</v>
       </c>
       <c r="B71" s="19" t="n"/>
       <c r="C71" s="41" t="n"/>
@@ -3529,7 +3529,7 @@
     </row>
     <row r="72" hidden="1" outlineLevel="2">
       <c r="A72" s="38" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="B72" s="19" t="n"/>
       <c r="C72" s="41" t="n"/>
@@ -3539,7 +3539,7 @@
     </row>
     <row r="73" hidden="1" outlineLevel="2">
       <c r="A73" s="38" t="n">
-        <v>16.75</v>
+        <v>17.75</v>
       </c>
       <c r="B73" s="19" t="n"/>
       <c r="C73" s="41" t="n"/>
@@ -3549,7 +3549,7 @@
     </row>
     <row r="74" collapsed="1" ht="57.6" customHeight="1">
       <c r="A74" s="38" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B74" s="19" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="75" hidden="1" outlineLevel="2">
       <c r="A75" s="38" t="n">
-        <v>17.25</v>
+        <v>18.25</v>
       </c>
       <c r="B75" s="19" t="n"/>
       <c r="C75" s="41" t="n"/>
@@ -3584,7 +3584,7 @@
     </row>
     <row r="76" hidden="1" outlineLevel="2">
       <c r="A76" s="38" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="B76" s="19" t="n"/>
       <c r="C76" s="41" t="n"/>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="77" hidden="1" outlineLevel="2">
       <c r="A77" s="38" t="n">
-        <v>17.75</v>
+        <v>18.75</v>
       </c>
       <c r="B77" s="19" t="n"/>
       <c r="C77" s="41" t="n"/>
@@ -3604,7 +3604,7 @@
     </row>
     <row r="78" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A78" s="38" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B78" s="19" t="n"/>
       <c r="C78" s="41" t="n"/>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="79" hidden="1" outlineLevel="2">
       <c r="A79" s="38" t="n">
-        <v>18.25</v>
+        <v>19.25</v>
       </c>
       <c r="B79" s="19" t="n"/>
       <c r="C79" s="41" t="n"/>
@@ -3624,7 +3624,7 @@
     </row>
     <row r="80" hidden="1" outlineLevel="2">
       <c r="A80" s="38" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="B80" s="19" t="n"/>
       <c r="C80" s="41" t="n"/>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="81" hidden="1" outlineLevel="2">
       <c r="A81" s="38" t="n">
-        <v>18.75</v>
+        <v>19.75</v>
       </c>
       <c r="B81" s="19" t="n"/>
       <c r="C81" s="41" t="n"/>
@@ -3644,7 +3644,7 @@
     </row>
     <row r="82" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A82" s="38" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B82" s="19" t="n"/>
       <c r="C82" s="41" t="n"/>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="83" hidden="1" outlineLevel="2">
       <c r="A83" s="38" t="n">
-        <v>19.25</v>
+        <v>20.25</v>
       </c>
       <c r="B83" s="19" t="n"/>
       <c r="C83" s="41" t="n"/>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="84" hidden="1" outlineLevel="2">
       <c r="A84" s="38" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
       <c r="B84" s="19" t="n"/>
       <c r="C84" s="41" t="n"/>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="85" hidden="1" outlineLevel="2">
       <c r="A85" s="38" t="n">
-        <v>19.75</v>
+        <v>20.75</v>
       </c>
       <c r="B85" s="19" t="n"/>
       <c r="C85" s="41" t="n"/>
@@ -3684,7 +3684,7 @@
     </row>
     <row r="86" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A86" s="38" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B86" s="19" t="n"/>
       <c r="C86" s="41" t="n"/>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="87" hidden="1" outlineLevel="2">
       <c r="A87" s="38" t="n">
-        <v>20.25</v>
+        <v>21.25</v>
       </c>
       <c r="B87" s="19" t="n"/>
       <c r="C87" s="41" t="n"/>
@@ -3704,7 +3704,7 @@
     </row>
     <row r="88" hidden="1" outlineLevel="2">
       <c r="A88" s="38" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="B88" s="19" t="n"/>
       <c r="C88" s="41" t="n"/>
@@ -3714,7 +3714,7 @@
     </row>
     <row r="89" hidden="1" outlineLevel="2">
       <c r="A89" s="38" t="n">
-        <v>20.75</v>
+        <v>21.75</v>
       </c>
       <c r="B89" s="19" t="n"/>
       <c r="C89" s="41" t="n"/>
@@ -3724,7 +3724,7 @@
     </row>
     <row r="90" collapsed="1" ht="43.2" customHeight="1">
       <c r="A90" s="38" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B90" s="19" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="91" hidden="1" outlineLevel="2">
       <c r="A91" s="38" t="n">
-        <v>21.25</v>
+        <v>22.25</v>
       </c>
       <c r="B91" s="19" t="n"/>
       <c r="C91" s="41" t="n"/>
@@ -3758,7 +3758,7 @@
     </row>
     <row r="92" hidden="1" outlineLevel="2">
       <c r="A92" s="38" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="B92" s="19" t="n"/>
       <c r="C92" s="41" t="n"/>
@@ -3768,7 +3768,7 @@
     </row>
     <row r="93" ht="28.8" customHeight="1">
       <c r="A93" s="38" t="n">
-        <v>21.75</v>
+        <v>22.75</v>
       </c>
       <c r="B93" s="19" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
     </row>
     <row r="94" collapsed="1" ht="43.2" customHeight="1">
       <c r="A94" s="38" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B94" s="19" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
     </row>
     <row r="95" hidden="1" outlineLevel="2">
       <c r="A95" s="38" t="n">
-        <v>22.25</v>
+        <v>23.25</v>
       </c>
       <c r="B95" s="19" t="n"/>
       <c r="C95" s="41" t="n"/>
@@ -3826,7 +3826,7 @@
     </row>
     <row r="96" hidden="1" outlineLevel="2">
       <c r="A96" s="38" t="n">
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="B96" s="19" t="n"/>
       <c r="C96" s="41" t="n"/>
@@ -3836,7 +3836,7 @@
     </row>
     <row r="97" hidden="1" outlineLevel="2">
       <c r="A97" s="38" t="n">
-        <v>22.75</v>
+        <v>23.75</v>
       </c>
       <c r="B97" s="19" t="n"/>
       <c r="C97" s="41" t="n"/>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="98" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A98" s="38" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B98" s="19" t="n"/>
       <c r="C98" s="41" t="n"/>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="99" hidden="1" outlineLevel="2">
       <c r="A99" s="38" t="n">
-        <v>23.25</v>
+        <v>24.25</v>
       </c>
       <c r="B99" s="19" t="n"/>
       <c r="C99" s="41" t="n"/>
@@ -3866,7 +3866,7 @@
     </row>
     <row r="100" hidden="1" outlineLevel="2">
       <c r="A100" s="38" t="n">
-        <v>23.5</v>
+        <v>24.5</v>
       </c>
       <c r="B100" s="19" t="n"/>
       <c r="C100" s="41" t="n"/>
@@ -3876,7 +3876,7 @@
     </row>
     <row r="101" hidden="1" outlineLevel="2">
       <c r="A101" s="38" t="n">
-        <v>23.75</v>
+        <v>24.75</v>
       </c>
       <c r="B101" s="19" t="n"/>
       <c r="C101" s="41" t="n"/>
@@ -3886,7 +3886,7 @@
     </row>
     <row r="102" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A102" s="38" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B102" s="19" t="n"/>
       <c r="C102" s="41" t="n"/>
@@ -3896,7 +3896,7 @@
     </row>
     <row r="103" hidden="1" outlineLevel="2">
       <c r="A103" s="38" t="n">
-        <v>24.25</v>
+        <v>25.25</v>
       </c>
       <c r="B103" s="19" t="n"/>
       <c r="C103" s="41" t="n"/>
@@ -3906,7 +3906,7 @@
     </row>
     <row r="104" hidden="1" outlineLevel="2">
       <c r="A104" s="38" t="n">
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
       <c r="B104" s="19" t="n"/>
       <c r="C104" s="41" t="n"/>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="105" hidden="1" outlineLevel="2">
       <c r="A105" s="38" t="n">
-        <v>24.75</v>
+        <v>25.75</v>
       </c>
       <c r="B105" s="19" t="n"/>
       <c r="C105" s="41" t="n"/>
@@ -3926,7 +3926,7 @@
     </row>
     <row r="106" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A106" s="38" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B106" s="19" t="n"/>
       <c r="C106" s="41" t="n"/>
@@ -3936,7 +3936,7 @@
     </row>
     <row r="107" hidden="1" outlineLevel="2">
       <c r="A107" s="38" t="n">
-        <v>25.25</v>
+        <v>26.25</v>
       </c>
       <c r="B107" s="19" t="n"/>
       <c r="C107" s="41" t="n"/>
@@ -3946,7 +3946,7 @@
     </row>
     <row r="108" hidden="1" outlineLevel="2">
       <c r="A108" s="38" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="B108" s="19" t="n"/>
       <c r="C108" s="41" t="n"/>
@@ -3956,7 +3956,7 @@
     </row>
     <row r="109" hidden="1" outlineLevel="2">
       <c r="A109" s="38" t="n">
-        <v>25.75</v>
+        <v>26.75</v>
       </c>
       <c r="B109" s="19" t="n"/>
       <c r="C109" s="41" t="n"/>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="110" collapsed="1" ht="144" customHeight="1">
       <c r="A110" s="38" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B110" s="19" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
     </row>
     <row r="111" hidden="1" outlineLevel="2">
       <c r="A111" s="38" t="n">
-        <v>26.25</v>
+        <v>27.25</v>
       </c>
       <c r="B111" s="19" t="n"/>
       <c r="C111" s="41" t="n"/>
@@ -4002,7 +4002,7 @@
     </row>
     <row r="112" hidden="1" outlineLevel="2">
       <c r="A112" s="38" t="n">
-        <v>26.5</v>
+        <v>27.5</v>
       </c>
       <c r="B112" s="19" t="n"/>
       <c r="C112" s="41" t="n"/>
@@ -4012,7 +4012,7 @@
     </row>
     <row r="113" hidden="1" outlineLevel="2">
       <c r="A113" s="38" t="n">
-        <v>26.75</v>
+        <v>27.75</v>
       </c>
       <c r="B113" s="19" t="n"/>
       <c r="C113" s="41" t="n"/>
@@ -4022,7 +4022,7 @@
     </row>
     <row r="114" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A114" s="38" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B114" s="19" t="n"/>
       <c r="C114" s="41" t="n"/>
@@ -4032,7 +4032,7 @@
     </row>
     <row r="115" hidden="1" outlineLevel="2">
       <c r="A115" s="38" t="n">
-        <v>27.25</v>
+        <v>28.25</v>
       </c>
       <c r="B115" s="19" t="n"/>
       <c r="C115" s="41" t="n"/>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="116" hidden="1" outlineLevel="2">
       <c r="A116" s="38" t="n">
-        <v>27.5</v>
+        <v>28.5</v>
       </c>
       <c r="B116" s="19" t="n"/>
       <c r="C116" s="41" t="n"/>
@@ -4052,7 +4052,7 @@
     </row>
     <row r="117" hidden="1" outlineLevel="2">
       <c r="A117" s="38" t="n">
-        <v>27.75</v>
+        <v>28.75</v>
       </c>
       <c r="B117" s="19" t="n"/>
       <c r="C117" s="41" t="n"/>
@@ -4062,7 +4062,7 @@
     </row>
     <row r="118" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A118" s="38" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B118" s="19" t="n"/>
       <c r="C118" s="41" t="n"/>
@@ -4072,7 +4072,7 @@
     </row>
     <row r="119" hidden="1" outlineLevel="2">
       <c r="A119" s="38" t="n">
-        <v>28.25</v>
+        <v>29.25</v>
       </c>
       <c r="B119" s="19" t="n"/>
       <c r="C119" s="41" t="n"/>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="120" hidden="1" outlineLevel="2">
       <c r="A120" s="38" t="n">
-        <v>28.5</v>
+        <v>29.5</v>
       </c>
       <c r="B120" s="19" t="n"/>
       <c r="C120" s="41" t="n"/>
@@ -4092,7 +4092,7 @@
     </row>
     <row r="121" hidden="1" outlineLevel="2">
       <c r="A121" s="38" t="n">
-        <v>28.75</v>
+        <v>29.75</v>
       </c>
       <c r="B121" s="19" t="n"/>
       <c r="C121" s="41" t="n"/>
@@ -4102,7 +4102,7 @@
     </row>
     <row r="122" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A122" s="38" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B122" s="19" t="n"/>
       <c r="C122" s="41" t="n"/>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="123" hidden="1" outlineLevel="2">
       <c r="A123" s="38" t="n">
-        <v>29.25</v>
+        <v>30.25</v>
       </c>
       <c r="B123" s="19" t="n"/>
       <c r="C123" s="41" t="n"/>
@@ -4122,7 +4122,7 @@
     </row>
     <row r="124" hidden="1" outlineLevel="2">
       <c r="A124" s="38" t="n">
-        <v>29.5</v>
+        <v>30.5</v>
       </c>
       <c r="B124" s="19" t="n"/>
       <c r="C124" s="41" t="n"/>
@@ -4132,7 +4132,7 @@
     </row>
     <row r="125" hidden="1" outlineLevel="2">
       <c r="A125" s="38" t="n">
-        <v>29.75</v>
+        <v>30.75</v>
       </c>
       <c r="B125" s="19" t="n"/>
       <c r="C125" s="41" t="n"/>
@@ -4142,7 +4142,7 @@
     </row>
     <row r="126" collapsed="1" ht="57.6" customHeight="1">
       <c r="A126" s="38" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B126" s="19" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="127" hidden="1" outlineLevel="2">
       <c r="A127" s="38" t="n">
-        <v>30.25</v>
+        <v>31.25</v>
       </c>
       <c r="B127" s="19" t="n"/>
       <c r="C127" s="41" t="n"/>
@@ -4177,7 +4177,7 @@
     </row>
     <row r="128" hidden="1" outlineLevel="2">
       <c r="A128" s="38" t="n">
-        <v>30.5</v>
+        <v>31.5</v>
       </c>
       <c r="B128" s="19" t="n"/>
       <c r="C128" s="41" t="n"/>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="129" hidden="1" outlineLevel="2">
       <c r="A129" s="38" t="n">
-        <v>30.75</v>
+        <v>31.75</v>
       </c>
       <c r="B129" s="19" t="n"/>
       <c r="C129" s="41" t="n"/>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="130" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A130" s="38" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B130" s="19" t="n"/>
       <c r="C130" s="41" t="n"/>
@@ -4207,7 +4207,7 @@
     </row>
     <row r="131" hidden="1" outlineLevel="2">
       <c r="A131" s="38" t="n">
-        <v>31.25</v>
+        <v>32.25</v>
       </c>
       <c r="B131" s="19" t="n"/>
       <c r="C131" s="41" t="n"/>
@@ -4217,7 +4217,7 @@
     </row>
     <row r="132" hidden="1" outlineLevel="2">
       <c r="A132" s="38" t="n">
-        <v>31.5</v>
+        <v>32.5</v>
       </c>
       <c r="B132" s="19" t="n"/>
       <c r="C132" s="41" t="n"/>
@@ -4227,7 +4227,7 @@
     </row>
     <row r="133" hidden="1" outlineLevel="2">
       <c r="A133" s="38" t="n">
-        <v>31.75</v>
+        <v>32.75</v>
       </c>
       <c r="B133" s="19" t="n"/>
       <c r="C133" s="41" t="n"/>
@@ -4237,7 +4237,7 @@
     </row>
     <row r="134" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A134" s="38" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B134" s="19" t="n"/>
       <c r="C134" s="41" t="n"/>
@@ -4247,7 +4247,7 @@
     </row>
     <row r="135" hidden="1" outlineLevel="2">
       <c r="A135" s="38" t="n">
-        <v>32.25</v>
+        <v>33.25</v>
       </c>
       <c r="B135" s="19" t="n"/>
       <c r="C135" s="41" t="n"/>
@@ -4257,7 +4257,7 @@
     </row>
     <row r="136" hidden="1" outlineLevel="2">
       <c r="A136" s="38" t="n">
-        <v>32.5</v>
+        <v>33.5</v>
       </c>
       <c r="B136" s="19" t="n"/>
       <c r="C136" s="41" t="n"/>
@@ -4267,7 +4267,7 @@
     </row>
     <row r="137" hidden="1" outlineLevel="2">
       <c r="A137" s="38" t="n">
-        <v>32.75</v>
+        <v>33.75</v>
       </c>
       <c r="B137" s="19" t="n"/>
       <c r="C137" s="41" t="n"/>
@@ -4277,7 +4277,7 @@
     </row>
     <row r="138" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A138" s="38" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B138" s="19" t="n"/>
       <c r="C138" s="41" t="n"/>
@@ -4287,7 +4287,7 @@
     </row>
     <row r="139" hidden="1" outlineLevel="2">
       <c r="A139" s="38" t="n">
-        <v>33.25</v>
+        <v>34.25</v>
       </c>
       <c r="B139" s="19" t="n"/>
       <c r="C139" s="41" t="n"/>
@@ -4297,7 +4297,7 @@
     </row>
     <row r="140" hidden="1" outlineLevel="2">
       <c r="A140" s="38" t="n">
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
       <c r="B140" s="19" t="n"/>
       <c r="C140" s="41" t="n"/>
@@ -4307,7 +4307,7 @@
     </row>
     <row r="141" hidden="1" outlineLevel="2">
       <c r="A141" s="38" t="n">
-        <v>33.75</v>
+        <v>34.75</v>
       </c>
       <c r="B141" s="19" t="n"/>
       <c r="C141" s="41" t="n"/>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="142" collapsed="1" ht="43.2" customHeight="1">
       <c r="A142" s="38" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B142" s="19" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
     </row>
     <row r="143" hidden="1" outlineLevel="2">
       <c r="A143" s="38" t="n">
-        <v>34.25</v>
+        <v>35.25</v>
       </c>
       <c r="B143" s="19" t="n"/>
       <c r="C143" s="41" t="n"/>
@@ -4351,7 +4351,7 @@
     </row>
     <row r="144" hidden="1" outlineLevel="2">
       <c r="A144" s="38" t="n">
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="B144" s="19" t="n"/>
       <c r="C144" s="41" t="n"/>
@@ -4361,7 +4361,7 @@
     </row>
     <row r="145" hidden="1" outlineLevel="2">
       <c r="A145" s="38" t="n">
-        <v>34.75</v>
+        <v>35.75</v>
       </c>
       <c r="B145" s="19" t="n"/>
       <c r="C145" s="41" t="n"/>
@@ -4371,7 +4371,7 @@
     </row>
     <row r="146" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A146" s="38" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B146" s="19" t="n"/>
       <c r="C146" s="41" t="n"/>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="147" hidden="1" outlineLevel="2">
       <c r="A147" s="38" t="n">
-        <v>35.25</v>
+        <v>36.25</v>
       </c>
       <c r="B147" s="19" t="n"/>
       <c r="C147" s="41" t="n"/>
@@ -4391,7 +4391,7 @@
     </row>
     <row r="148" hidden="1" outlineLevel="2">
       <c r="A148" s="38" t="n">
-        <v>35.5</v>
+        <v>36.5</v>
       </c>
       <c r="B148" s="19" t="n"/>
       <c r="C148" s="41" t="n"/>
@@ -4401,7 +4401,7 @@
     </row>
     <row r="149" hidden="1" outlineLevel="2">
       <c r="A149" s="38" t="n">
-        <v>35.75</v>
+        <v>36.75</v>
       </c>
       <c r="B149" s="19" t="n"/>
       <c r="C149" s="41" t="n"/>
@@ -4411,7 +4411,7 @@
     </row>
     <row r="150" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A150" s="38" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B150" s="19" t="n"/>
       <c r="C150" s="41" t="n"/>
@@ -4421,7 +4421,7 @@
     </row>
     <row r="151" hidden="1" outlineLevel="2">
       <c r="A151" s="38" t="n">
-        <v>36.25</v>
+        <v>37.25</v>
       </c>
       <c r="B151" s="19" t="n"/>
       <c r="C151" s="41" t="n"/>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="152" hidden="1" outlineLevel="2">
       <c r="A152" s="38" t="n">
-        <v>36.5</v>
+        <v>37.5</v>
       </c>
       <c r="B152" s="19" t="n"/>
       <c r="C152" s="41" t="n"/>
@@ -4441,7 +4441,7 @@
     </row>
     <row r="153" hidden="1" outlineLevel="2">
       <c r="A153" s="38" t="n">
-        <v>36.75</v>
+        <v>37.75</v>
       </c>
       <c r="B153" s="19" t="n"/>
       <c r="C153" s="41" t="n"/>
@@ -4451,7 +4451,7 @@
     </row>
     <row r="154" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A154" s="38" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B154" s="19" t="n"/>
       <c r="C154" s="41" t="n"/>
@@ -4461,7 +4461,7 @@
     </row>
     <row r="155" hidden="1" outlineLevel="2">
       <c r="A155" s="38" t="n">
-        <v>37.25</v>
+        <v>38.25</v>
       </c>
       <c r="B155" s="19" t="n"/>
       <c r="C155" s="41" t="n"/>
@@ -4471,7 +4471,7 @@
     </row>
     <row r="156" hidden="1" outlineLevel="2">
       <c r="A156" s="38" t="n">
-        <v>37.5</v>
+        <v>38.5</v>
       </c>
       <c r="B156" s="19" t="n"/>
       <c r="C156" s="41" t="n"/>
@@ -4481,7 +4481,7 @@
     </row>
     <row r="157" hidden="1" outlineLevel="2">
       <c r="A157" s="38" t="n">
-        <v>37.75</v>
+        <v>38.75</v>
       </c>
       <c r="B157" s="19" t="n"/>
       <c r="C157" s="41" t="n"/>
@@ -4491,7 +4491,7 @@
     </row>
     <row r="158" collapsed="1" ht="86.40000000000001" customHeight="1">
       <c r="A158" s="38" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B158" s="19" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
     </row>
     <row r="159" hidden="1" outlineLevel="2">
       <c r="A159" s="38" t="n">
-        <v>38.25</v>
+        <v>39.25</v>
       </c>
       <c r="B159" s="19" t="n"/>
       <c r="C159" s="41" t="n"/>
@@ -4527,7 +4527,7 @@
     </row>
     <row r="160" hidden="1" outlineLevel="2">
       <c r="A160" s="38" t="n">
-        <v>38.5</v>
+        <v>39.5</v>
       </c>
       <c r="B160" s="19" t="n"/>
       <c r="C160" s="41" t="n"/>
@@ -4537,7 +4537,7 @@
     </row>
     <row r="161" hidden="1" outlineLevel="2">
       <c r="A161" s="38" t="n">
-        <v>38.75</v>
+        <v>39.75</v>
       </c>
       <c r="B161" s="19" t="n"/>
       <c r="C161" s="41" t="n"/>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="162" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A162" s="38" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B162" s="19" t="n"/>
       <c r="C162" s="41" t="n"/>
@@ -4557,7 +4557,7 @@
     </row>
     <row r="163" hidden="1" outlineLevel="2">
       <c r="A163" s="38" t="n">
-        <v>39.25</v>
+        <v>40.25</v>
       </c>
       <c r="B163" s="19" t="n"/>
       <c r="C163" s="41" t="n"/>
@@ -4567,7 +4567,7 @@
     </row>
     <row r="164" hidden="1" outlineLevel="2">
       <c r="A164" s="38" t="n">
-        <v>39.5</v>
+        <v>40.5</v>
       </c>
       <c r="B164" s="19" t="n"/>
       <c r="C164" s="41" t="n"/>
@@ -4577,7 +4577,7 @@
     </row>
     <row r="165" hidden="1" outlineLevel="2">
       <c r="A165" s="38" t="n">
-        <v>39.75</v>
+        <v>40.75</v>
       </c>
       <c r="B165" s="19" t="n"/>
       <c r="C165" s="41" t="n"/>
@@ -4587,7 +4587,7 @@
     </row>
     <row r="166" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A166" s="38" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B166" s="19" t="n"/>
       <c r="C166" s="41" t="n"/>
@@ -4597,7 +4597,7 @@
     </row>
     <row r="167" hidden="1" outlineLevel="2">
       <c r="A167" s="38" t="n">
-        <v>40.25</v>
+        <v>41.25</v>
       </c>
       <c r="B167" s="19" t="n"/>
       <c r="C167" s="41" t="n"/>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="168" hidden="1" outlineLevel="2">
       <c r="A168" s="38" t="n">
-        <v>40.5</v>
+        <v>41.5</v>
       </c>
       <c r="B168" s="19" t="n"/>
       <c r="C168" s="41" t="n"/>
@@ -4617,7 +4617,7 @@
     </row>
     <row r="169" hidden="1" outlineLevel="2">
       <c r="A169" s="38" t="n">
-        <v>40.75</v>
+        <v>41.75</v>
       </c>
       <c r="B169" s="19" t="n"/>
       <c r="C169" s="41" t="n"/>
@@ -4627,7 +4627,7 @@
     </row>
     <row r="170" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A170" s="38" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B170" s="19" t="n"/>
       <c r="C170" s="41" t="n"/>
@@ -4637,7 +4637,7 @@
     </row>
     <row r="171" hidden="1" outlineLevel="2">
       <c r="A171" s="38" t="n">
-        <v>41.25</v>
+        <v>42.25</v>
       </c>
       <c r="B171" s="19" t="n"/>
       <c r="C171" s="41" t="n"/>
@@ -4647,7 +4647,7 @@
     </row>
     <row r="172" hidden="1" outlineLevel="2">
       <c r="A172" s="38" t="n">
-        <v>41.5</v>
+        <v>42.5</v>
       </c>
       <c r="B172" s="19" t="n"/>
       <c r="C172" s="41" t="n"/>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="173" hidden="1" outlineLevel="2">
       <c r="A173" s="38" t="n">
-        <v>41.75</v>
+        <v>42.75</v>
       </c>
       <c r="B173" s="19" t="n"/>
       <c r="C173" s="41" t="n"/>
@@ -4667,7 +4667,7 @@
     </row>
     <row r="174" collapsed="1" ht="57.6" customHeight="1">
       <c r="A174" s="38" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B174" s="19" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
     </row>
     <row r="175" hidden="1" outlineLevel="2">
       <c r="A175" s="38" t="n">
-        <v>42.25</v>
+        <v>43.25</v>
       </c>
       <c r="B175" s="19" t="n"/>
       <c r="C175" s="41" t="n"/>
@@ -4701,7 +4701,7 @@
     </row>
     <row r="176" hidden="1" outlineLevel="2">
       <c r="A176" s="38" t="n">
-        <v>42.5</v>
+        <v>43.5</v>
       </c>
       <c r="B176" s="19" t="n"/>
       <c r="C176" s="41" t="n"/>
@@ -4711,7 +4711,7 @@
     </row>
     <row r="177" hidden="1" outlineLevel="2">
       <c r="A177" s="38" t="n">
-        <v>42.75</v>
+        <v>43.75</v>
       </c>
       <c r="B177" s="19" t="n"/>
       <c r="C177" s="41" t="n"/>
@@ -4721,7 +4721,7 @@
     </row>
     <row r="178" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A178" s="38" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B178" s="19" t="n"/>
       <c r="C178" s="41" t="n"/>
@@ -4731,7 +4731,7 @@
     </row>
     <row r="179" hidden="1" outlineLevel="2">
       <c r="A179" s="38" t="n">
-        <v>43.25</v>
+        <v>44.25</v>
       </c>
       <c r="B179" s="19" t="n"/>
       <c r="C179" s="41" t="n"/>
@@ -4741,7 +4741,7 @@
     </row>
     <row r="180" hidden="1" outlineLevel="2">
       <c r="A180" s="38" t="n">
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
       <c r="B180" s="19" t="n"/>
       <c r="C180" s="41" t="n"/>
@@ -4751,7 +4751,7 @@
     </row>
     <row r="181" hidden="1" outlineLevel="2">
       <c r="A181" s="38" t="n">
-        <v>43.75</v>
+        <v>44.75</v>
       </c>
       <c r="B181" s="19" t="n"/>
       <c r="C181" s="41" t="n"/>
@@ -4761,7 +4761,7 @@
     </row>
     <row r="182" collapsed="1" ht="43.2" customHeight="1">
       <c r="A182" s="38" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B182" s="19" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
     </row>
     <row r="183" hidden="1" outlineLevel="2">
       <c r="A183" s="38" t="n">
-        <v>44.25</v>
+        <v>45.25</v>
       </c>
       <c r="B183" s="19" t="n"/>
       <c r="C183" s="41" t="n"/>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="184" hidden="1" outlineLevel="2">
       <c r="A184" s="38" t="n">
-        <v>44.5</v>
+        <v>45.5</v>
       </c>
       <c r="B184" s="19" t="n"/>
       <c r="C184" s="41" t="n"/>
@@ -4805,7 +4805,7 @@
     </row>
     <row r="185" hidden="1" outlineLevel="2">
       <c r="A185" s="38" t="n">
-        <v>44.75</v>
+        <v>45.75</v>
       </c>
       <c r="B185" s="19" t="n"/>
       <c r="C185" s="41" t="n"/>
@@ -4815,7 +4815,7 @@
     </row>
     <row r="186" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A186" s="38" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B186" s="19" t="n"/>
       <c r="C186" s="41" t="n"/>
@@ -4825,7 +4825,7 @@
     </row>
     <row r="187" hidden="1" outlineLevel="2">
       <c r="A187" s="38" t="n">
-        <v>45.25</v>
+        <v>46.25</v>
       </c>
       <c r="B187" s="19" t="n"/>
       <c r="C187" s="41" t="n"/>
@@ -4835,7 +4835,7 @@
     </row>
     <row r="188" collapsed="1" ht="28.8" customHeight="1">
       <c r="A188" s="38" t="n">
-        <v>45.5</v>
+        <v>46.5</v>
       </c>
       <c r="B188" s="19" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
     </row>
     <row r="189" hidden="1" outlineLevel="2">
       <c r="A189" s="38" t="n">
-        <v>45.75</v>
+        <v>46.75</v>
       </c>
       <c r="B189" s="19" t="n"/>
       <c r="C189" s="41" t="n"/>
@@ -4869,7 +4869,7 @@
     </row>
     <row r="190" collapsed="1" ht="28.8" customHeight="1">
       <c r="A190" s="38" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B190" s="19" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
     </row>
     <row r="191" hidden="1" outlineLevel="2">
       <c r="A191" s="38" t="n">
-        <v>46.25</v>
+        <v>47.25</v>
       </c>
       <c r="B191" s="19" t="n"/>
       <c r="C191" s="41" t="n"/>
@@ -4903,7 +4903,7 @@
     </row>
     <row r="192" hidden="1" outlineLevel="2">
       <c r="A192" s="38" t="n">
-        <v>46.5</v>
+        <v>47.5</v>
       </c>
       <c r="B192" s="19" t="n"/>
       <c r="C192" s="41" t="n"/>
@@ -4913,7 +4913,7 @@
     </row>
     <row r="193" hidden="1" outlineLevel="2">
       <c r="A193" s="38" t="n">
-        <v>46.75</v>
+        <v>47.75</v>
       </c>
       <c r="B193" s="19" t="n"/>
       <c r="C193" s="41" t="n"/>
@@ -4923,7 +4923,7 @@
     </row>
     <row r="194" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A194" s="38" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B194" s="19" t="n"/>
       <c r="C194" s="41" t="n"/>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="195" hidden="1" outlineLevel="2">
       <c r="A195" s="38" t="n">
-        <v>47.25</v>
+        <v>48.25</v>
       </c>
       <c r="B195" s="19" t="n"/>
       <c r="C195" s="41" t="n"/>
@@ -4943,7 +4943,7 @@
     </row>
     <row r="196" hidden="1" outlineLevel="2">
       <c r="A196" s="38" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="B196" s="19" t="n"/>
       <c r="C196" s="41" t="n"/>
@@ -4953,7 +4953,7 @@
     </row>
     <row r="197" hidden="1" outlineLevel="2">
       <c r="A197" s="38" t="n">
-        <v>47.75</v>
+        <v>48.75</v>
       </c>
       <c r="B197" s="19" t="n"/>
       <c r="C197" s="41" t="n"/>
@@ -4963,7 +4963,7 @@
     </row>
     <row r="198" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A198" s="38" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B198" s="19" t="n"/>
       <c r="C198" s="41" t="n"/>
@@ -4973,7 +4973,7 @@
     </row>
     <row r="199" hidden="1" outlineLevel="2">
       <c r="A199" s="38" t="n">
-        <v>48.25</v>
+        <v>49.25</v>
       </c>
       <c r="B199" s="19" t="n"/>
       <c r="C199" s="41" t="n"/>
@@ -4983,7 +4983,7 @@
     </row>
     <row r="200" hidden="1" outlineLevel="2">
       <c r="A200" s="38" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="B200" s="19" t="n"/>
       <c r="C200" s="41" t="n"/>
@@ -4993,7 +4993,7 @@
     </row>
     <row r="201" hidden="1" outlineLevel="2">
       <c r="A201" s="38" t="n">
-        <v>48.75</v>
+        <v>49.75</v>
       </c>
       <c r="B201" s="19" t="n"/>
       <c r="C201" s="41" t="n"/>
@@ -5003,7 +5003,7 @@
     </row>
     <row r="202" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A202" s="38" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B202" s="19" t="n"/>
       <c r="C202" s="41" t="n"/>
@@ -5013,7 +5013,7 @@
     </row>
     <row r="203" hidden="1" outlineLevel="2">
       <c r="A203" s="38" t="n">
-        <v>49.25</v>
+        <v>50.25</v>
       </c>
       <c r="B203" s="19" t="n"/>
       <c r="C203" s="41" t="n"/>
@@ -5023,7 +5023,7 @@
     </row>
     <row r="204" hidden="1" outlineLevel="2">
       <c r="A204" s="38" t="n">
-        <v>49.5</v>
+        <v>50.5</v>
       </c>
       <c r="B204" s="19" t="n"/>
       <c r="C204" s="41" t="n"/>
@@ -5033,7 +5033,7 @@
     </row>
     <row r="205" hidden="1" outlineLevel="2">
       <c r="A205" s="38" t="n">
-        <v>49.75</v>
+        <v>50.75</v>
       </c>
       <c r="B205" s="19" t="n"/>
       <c r="C205" s="41" t="n"/>
@@ -5043,7 +5043,7 @@
     </row>
     <row r="206" collapsed="1" ht="129.6" customHeight="1">
       <c r="A206" s="38" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B206" s="19" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
     </row>
     <row r="207" hidden="1" outlineLevel="2">
       <c r="A207" s="38" t="n">
-        <v>50.25</v>
+        <v>51.25</v>
       </c>
       <c r="B207" s="19" t="n"/>
       <c r="C207" s="41" t="n"/>
@@ -5079,7 +5079,7 @@
     </row>
     <row r="208" hidden="1" outlineLevel="2">
       <c r="A208" s="38" t="n">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
       <c r="B208" s="19" t="n"/>
       <c r="C208" s="41" t="n"/>
@@ -5089,7 +5089,7 @@
     </row>
     <row r="209" hidden="1" outlineLevel="2">
       <c r="A209" s="38" t="n">
-        <v>50.75</v>
+        <v>51.75</v>
       </c>
       <c r="B209" s="19" t="n"/>
       <c r="C209" s="41" t="n"/>
@@ -5099,7 +5099,7 @@
     </row>
     <row r="210" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A210" s="38" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B210" s="19" t="n"/>
       <c r="C210" s="41" t="n"/>
@@ -5109,7 +5109,7 @@
     </row>
     <row r="211" hidden="1" outlineLevel="2">
       <c r="A211" s="38" t="n">
-        <v>51.25</v>
+        <v>52.25</v>
       </c>
       <c r="B211" s="19" t="n"/>
       <c r="C211" s="41" t="n"/>
@@ -5119,7 +5119,7 @@
     </row>
     <row r="212" hidden="1" outlineLevel="2">
       <c r="A212" s="38" t="n">
-        <v>51.5</v>
+        <v>52.5</v>
       </c>
       <c r="B212" s="19" t="n"/>
       <c r="C212" s="41" t="n"/>
@@ -5129,7 +5129,7 @@
     </row>
     <row r="213" hidden="1" outlineLevel="2">
       <c r="A213" s="38" t="n">
-        <v>51.75</v>
+        <v>52.75</v>
       </c>
       <c r="B213" s="19" t="n"/>
       <c r="C213" s="41" t="n"/>
@@ -5139,7 +5139,7 @@
     </row>
     <row r="214" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A214" s="38" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B214" s="19" t="n"/>
       <c r="C214" s="41" t="n"/>
@@ -5149,7 +5149,7 @@
     </row>
     <row r="215" hidden="1" outlineLevel="2">
       <c r="A215" s="38" t="n">
-        <v>52.25</v>
+        <v>53.25</v>
       </c>
       <c r="B215" s="19" t="n"/>
       <c r="C215" s="41" t="n"/>
@@ -5159,7 +5159,7 @@
     </row>
     <row r="216" hidden="1" outlineLevel="2">
       <c r="A216" s="38" t="n">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="B216" s="19" t="n"/>
       <c r="C216" s="41" t="n"/>
@@ -5169,7 +5169,7 @@
     </row>
     <row r="217" hidden="1" outlineLevel="2">
       <c r="A217" s="38" t="n">
-        <v>52.75</v>
+        <v>53.75</v>
       </c>
       <c r="B217" s="19" t="n"/>
       <c r="C217" s="41" t="n"/>
@@ -5179,7 +5179,7 @@
     </row>
     <row r="218" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A218" s="38" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B218" s="19" t="n"/>
       <c r="C218" s="41" t="n"/>
@@ -5189,7 +5189,7 @@
     </row>
     <row r="219" hidden="1" outlineLevel="2">
       <c r="A219" s="38" t="n">
-        <v>53.25</v>
+        <v>54.25</v>
       </c>
       <c r="B219" s="19" t="n"/>
       <c r="C219" s="41" t="n"/>
@@ -5199,7 +5199,7 @@
     </row>
     <row r="220" hidden="1" outlineLevel="2">
       <c r="A220" s="38" t="n">
-        <v>53.5</v>
+        <v>54.5</v>
       </c>
       <c r="B220" s="19" t="n"/>
       <c r="C220" s="41" t="n"/>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="221" hidden="1" outlineLevel="2">
       <c r="A221" s="38" t="n">
-        <v>53.75</v>
+        <v>54.75</v>
       </c>
       <c r="B221" s="19" t="n"/>
       <c r="C221" s="41" t="n"/>
@@ -5219,7 +5219,7 @@
     </row>
     <row r="222" collapsed="1" ht="72" customHeight="1">
       <c r="A222" s="38" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B222" s="19" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
     </row>
     <row r="223" hidden="1" outlineLevel="2">
       <c r="A223" s="38" t="n">
-        <v>54.25</v>
+        <v>55.25</v>
       </c>
       <c r="B223" s="19" t="n"/>
       <c r="C223" s="41" t="n"/>
@@ -5254,7 +5254,7 @@
     </row>
     <row r="224" hidden="1" outlineLevel="2">
       <c r="A224" s="38" t="n">
-        <v>54.5</v>
+        <v>55.5</v>
       </c>
       <c r="B224" s="19" t="n"/>
       <c r="C224" s="41" t="n"/>
@@ -5264,7 +5264,7 @@
     </row>
     <row r="225" hidden="1" outlineLevel="2">
       <c r="A225" s="38" t="n">
-        <v>54.75</v>
+        <v>55.75</v>
       </c>
       <c r="B225" s="19" t="n"/>
       <c r="C225" s="41" t="n"/>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="226" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A226" s="38" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B226" s="19" t="n"/>
       <c r="C226" s="41" t="n"/>
@@ -5284,7 +5284,7 @@
     </row>
     <row r="227" hidden="1" outlineLevel="2">
       <c r="A227" s="38" t="n">
-        <v>55.25</v>
+        <v>56.25</v>
       </c>
       <c r="B227" s="19" t="n"/>
       <c r="C227" s="41" t="n"/>
@@ -5294,7 +5294,7 @@
     </row>
     <row r="228" hidden="1" outlineLevel="2">
       <c r="A228" s="38" t="n">
-        <v>55.5</v>
+        <v>56.5</v>
       </c>
       <c r="B228" s="19" t="n"/>
       <c r="C228" s="41" t="n"/>
@@ -5304,7 +5304,7 @@
     </row>
     <row r="229" hidden="1" outlineLevel="2">
       <c r="A229" s="38" t="n">
-        <v>55.75</v>
+        <v>56.75</v>
       </c>
       <c r="B229" s="19" t="n"/>
       <c r="C229" s="41" t="n"/>
@@ -5314,7 +5314,7 @@
     </row>
     <row r="230" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A230" s="38" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B230" s="19" t="n"/>
       <c r="C230" s="41" t="n"/>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="231" hidden="1" outlineLevel="2">
       <c r="A231" s="38" t="n">
-        <v>56.25</v>
+        <v>57.25</v>
       </c>
       <c r="B231" s="19" t="n"/>
       <c r="C231" s="41" t="n"/>
@@ -5334,7 +5334,7 @@
     </row>
     <row r="232" hidden="1" outlineLevel="2">
       <c r="A232" s="38" t="n">
-        <v>56.5</v>
+        <v>57.5</v>
       </c>
       <c r="B232" s="19" t="n"/>
       <c r="C232" s="41" t="n"/>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="233" hidden="1" outlineLevel="2">
       <c r="A233" s="38" t="n">
-        <v>56.75</v>
+        <v>57.75</v>
       </c>
       <c r="B233" s="19" t="n"/>
       <c r="C233" s="41" t="n"/>
@@ -5354,7 +5354,7 @@
     </row>
     <row r="234" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A234" s="38" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B234" s="19" t="n"/>
       <c r="C234" s="41" t="n"/>
@@ -5364,7 +5364,7 @@
     </row>
     <row r="235" hidden="1" outlineLevel="2">
       <c r="A235" s="38" t="n">
-        <v>57.25</v>
+        <v>58.25</v>
       </c>
       <c r="B235" s="19" t="n"/>
       <c r="C235" s="41" t="n"/>
@@ -5374,7 +5374,7 @@
     </row>
     <row r="236" hidden="1" outlineLevel="2">
       <c r="A236" s="38" t="n">
-        <v>57.5</v>
+        <v>58.5</v>
       </c>
       <c r="B236" s="19" t="n"/>
       <c r="C236" s="41" t="n"/>
@@ -5384,7 +5384,7 @@
     </row>
     <row r="237" hidden="1" outlineLevel="2">
       <c r="A237" s="38" t="n">
-        <v>57.75</v>
+        <v>58.75</v>
       </c>
       <c r="B237" s="19" t="n"/>
       <c r="C237" s="41" t="n"/>
@@ -5394,7 +5394,7 @@
     </row>
     <row r="238" collapsed="1" ht="57.6" customHeight="1">
       <c r="A238" s="38" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B238" s="19" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
     </row>
     <row r="239" hidden="1" outlineLevel="2">
       <c r="A239" s="38" t="n">
-        <v>58.25</v>
+        <v>59.25</v>
       </c>
       <c r="B239" s="19" t="n"/>
       <c r="C239" s="41" t="n"/>
@@ -5429,7 +5429,7 @@
     </row>
     <row r="240" hidden="1" outlineLevel="2">
       <c r="A240" s="38" t="n">
-        <v>58.5</v>
+        <v>59.5</v>
       </c>
       <c r="B240" s="19" t="n"/>
       <c r="C240" s="41" t="n"/>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="241" hidden="1" outlineLevel="2">
       <c r="A241" s="38" t="n">
-        <v>58.75</v>
+        <v>59.75</v>
       </c>
       <c r="B241" s="19" t="n"/>
       <c r="C241" s="41" t="n"/>
@@ -5449,7 +5449,7 @@
     </row>
     <row r="242" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A242" s="38" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B242" s="19" t="n"/>
       <c r="C242" s="41" t="n"/>
@@ -5459,7 +5459,7 @@
     </row>
     <row r="243" hidden="1" outlineLevel="2">
       <c r="A243" s="38" t="n">
-        <v>59.25</v>
+        <v>60.25</v>
       </c>
       <c r="B243" s="19" t="n"/>
       <c r="C243" s="41" t="n"/>
@@ -5469,7 +5469,7 @@
     </row>
     <row r="244" hidden="1" outlineLevel="2">
       <c r="A244" s="38" t="n">
-        <v>59.5</v>
+        <v>60.5</v>
       </c>
       <c r="B244" s="19" t="n"/>
       <c r="C244" s="41" t="n"/>
@@ -5479,7 +5479,7 @@
     </row>
     <row r="245" hidden="1" outlineLevel="2">
       <c r="A245" s="38" t="n">
-        <v>59.75</v>
+        <v>60.75</v>
       </c>
       <c r="B245" s="19" t="n"/>
       <c r="C245" s="41" t="n"/>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="246" collapsed="1" ht="43.2" customHeight="1">
       <c r="A246" s="38" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B246" s="19" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
     </row>
     <row r="247" hidden="1" outlineLevel="2">
       <c r="A247" s="38" t="n">
-        <v>60.25</v>
+        <v>61.25</v>
       </c>
       <c r="B247" s="19" t="n"/>
       <c r="C247" s="41" t="n"/>
@@ -5523,7 +5523,7 @@
     </row>
     <row r="248" hidden="1" outlineLevel="2">
       <c r="A248" s="38" t="n">
-        <v>60.5</v>
+        <v>61.5</v>
       </c>
       <c r="B248" s="19" t="n"/>
       <c r="C248" s="41" t="n"/>
@@ -5533,7 +5533,7 @@
     </row>
     <row r="249" hidden="1" outlineLevel="2">
       <c r="A249" s="38" t="n">
-        <v>60.75</v>
+        <v>61.75</v>
       </c>
       <c r="B249" s="19" t="n"/>
       <c r="C249" s="41" t="n"/>
@@ -5543,7 +5543,7 @@
     </row>
     <row r="250" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A250" s="38" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B250" s="19" t="n"/>
       <c r="C250" s="41" t="n"/>
@@ -5553,7 +5553,7 @@
     </row>
     <row r="251" hidden="1" outlineLevel="2">
       <c r="A251" s="38" t="n">
-        <v>61.25</v>
+        <v>62.25</v>
       </c>
       <c r="B251" s="19" t="n"/>
       <c r="C251" s="41" t="n"/>
@@ -5563,7 +5563,7 @@
     </row>
     <row r="252" collapsed="1" ht="28.8" customHeight="1">
       <c r="A252" s="38" t="n">
-        <v>61.5</v>
+        <v>62.5</v>
       </c>
       <c r="B252" s="19" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
     </row>
     <row r="253" hidden="1" outlineLevel="2">
       <c r="A253" s="38" t="n">
-        <v>61.75</v>
+        <v>62.75</v>
       </c>
       <c r="B253" s="19" t="n"/>
       <c r="C253" s="41" t="n"/>
@@ -5597,7 +5597,7 @@
     </row>
     <row r="254" collapsed="1" ht="28.8" customHeight="1">
       <c r="A254" s="38" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B254" s="19" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
     </row>
     <row r="255" hidden="1" outlineLevel="2">
       <c r="A255" s="38" t="n">
-        <v>62.25</v>
+        <v>63.25</v>
       </c>
       <c r="B255" s="19" t="n"/>
       <c r="C255" s="41" t="n"/>
@@ -5631,7 +5631,7 @@
     </row>
     <row r="256" collapsed="1" ht="28.8" customHeight="1">
       <c r="A256" s="38" t="n">
-        <v>62.5</v>
+        <v>63.5</v>
       </c>
       <c r="B256" s="19" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
     </row>
     <row r="257" hidden="1" outlineLevel="2">
       <c r="A257" s="38" t="n">
-        <v>62.75</v>
+        <v>63.75</v>
       </c>
       <c r="B257" s="19" t="n"/>
       <c r="C257" s="41" t="n"/>
@@ -5665,7 +5665,7 @@
     </row>
     <row r="258" collapsed="1" ht="43.2" customHeight="1">
       <c r="A258" s="38" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B258" s="19" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
     </row>
     <row r="259" hidden="1" outlineLevel="2">
       <c r="A259" s="38" t="n">
-        <v>63.25</v>
+        <v>64.25</v>
       </c>
       <c r="B259" s="19" t="n"/>
       <c r="C259" s="41" t="n"/>
@@ -5700,7 +5700,7 @@
     </row>
     <row r="260" hidden="1" outlineLevel="2">
       <c r="A260" s="38" t="n">
-        <v>63.5</v>
+        <v>64.5</v>
       </c>
       <c r="B260" s="19" t="n"/>
       <c r="C260" s="41" t="n"/>
@@ -5710,7 +5710,7 @@
     </row>
     <row r="261" hidden="1" outlineLevel="2">
       <c r="A261" s="38" t="n">
-        <v>63.75</v>
+        <v>64.75</v>
       </c>
       <c r="B261" s="19" t="n"/>
       <c r="C261" s="41" t="n"/>
@@ -5720,7 +5720,7 @@
     </row>
     <row r="262" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A262" s="38" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B262" s="19" t="n"/>
       <c r="C262" s="41" t="n"/>
@@ -5730,7 +5730,7 @@
     </row>
     <row r="263" hidden="1" outlineLevel="2">
       <c r="A263" s="38" t="n">
-        <v>64.25</v>
+        <v>65.25</v>
       </c>
       <c r="B263" s="19" t="n"/>
       <c r="C263" s="41" t="n"/>
@@ -5740,7 +5740,7 @@
     </row>
     <row r="264" hidden="1" outlineLevel="2">
       <c r="A264" s="38" t="n">
-        <v>64.5</v>
+        <v>65.5</v>
       </c>
       <c r="B264" s="19" t="n"/>
       <c r="C264" s="41" t="n"/>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="265" hidden="1" outlineLevel="2">
       <c r="A265" s="38" t="n">
-        <v>64.75</v>
+        <v>65.75</v>
       </c>
       <c r="B265" s="19" t="n"/>
       <c r="C265" s="41" t="n"/>
@@ -5760,7 +5760,7 @@
     </row>
     <row r="266" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A266" s="38" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B266" s="19" t="n"/>
       <c r="C266" s="41" t="n"/>
@@ -5770,7 +5770,7 @@
     </row>
     <row r="267" hidden="1" outlineLevel="2">
       <c r="A267" s="38" t="n">
-        <v>65.25</v>
+        <v>66.25</v>
       </c>
       <c r="B267" s="19" t="n"/>
       <c r="C267" s="41" t="n"/>
@@ -5780,7 +5780,7 @@
     </row>
     <row r="268" hidden="1" outlineLevel="2">
       <c r="A268" s="38" t="n">
-        <v>65.5</v>
+        <v>66.5</v>
       </c>
       <c r="B268" s="19" t="n"/>
       <c r="C268" s="41" t="n"/>
@@ -5790,7 +5790,7 @@
     </row>
     <row r="269" hidden="1" outlineLevel="2">
       <c r="A269" s="38" t="n">
-        <v>65.75</v>
+        <v>66.75</v>
       </c>
       <c r="B269" s="19" t="n"/>
       <c r="C269" s="41" t="n"/>
@@ -5800,7 +5800,7 @@
     </row>
     <row r="270" collapsed="1" ht="144" customHeight="1">
       <c r="A270" s="38" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B270" s="19" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
     </row>
     <row r="271" hidden="1" outlineLevel="2">
       <c r="A271" s="38" t="n">
-        <v>66.25</v>
+        <v>67.25</v>
       </c>
       <c r="B271" s="19" t="n"/>
       <c r="C271" s="41" t="n"/>
@@ -5836,7 +5836,7 @@
     </row>
     <row r="272" hidden="1" outlineLevel="2">
       <c r="A272" s="38" t="n">
-        <v>66.5</v>
+        <v>67.5</v>
       </c>
       <c r="B272" s="19" t="n"/>
       <c r="C272" s="41" t="n"/>
@@ -5846,7 +5846,7 @@
     </row>
     <row r="273" hidden="1" outlineLevel="2">
       <c r="A273" s="38" t="n">
-        <v>66.75</v>
+        <v>67.75</v>
       </c>
       <c r="B273" s="19" t="n"/>
       <c r="C273" s="41" t="n"/>
@@ -5856,7 +5856,7 @@
     </row>
     <row r="274" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A274" s="38" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B274" s="19" t="n"/>
       <c r="C274" s="41" t="n"/>
@@ -5866,7 +5866,7 @@
     </row>
     <row r="275" hidden="1" outlineLevel="2">
       <c r="A275" s="38" t="n">
-        <v>67.25</v>
+        <v>68.25</v>
       </c>
       <c r="B275" s="19" t="n"/>
       <c r="C275" s="41" t="n"/>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="276" hidden="1" outlineLevel="2">
       <c r="A276" s="38" t="n">
-        <v>67.5</v>
+        <v>68.5</v>
       </c>
       <c r="B276" s="19" t="n"/>
       <c r="C276" s="41" t="n"/>
@@ -5886,7 +5886,7 @@
     </row>
     <row r="277" hidden="1" outlineLevel="2">
       <c r="A277" s="38" t="n">
-        <v>67.75</v>
+        <v>68.75</v>
       </c>
       <c r="B277" s="19" t="n"/>
       <c r="C277" s="41" t="n"/>
@@ -5896,7 +5896,7 @@
     </row>
     <row r="278" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A278" s="38" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B278" s="19" t="n"/>
       <c r="C278" s="41" t="n"/>
@@ -5906,7 +5906,7 @@
     </row>
     <row r="279" hidden="1" outlineLevel="2">
       <c r="A279" s="38" t="n">
-        <v>68.25</v>
+        <v>69.25</v>
       </c>
       <c r="B279" s="19" t="n"/>
       <c r="C279" s="41" t="n"/>
@@ -5916,7 +5916,7 @@
     </row>
     <row r="280" hidden="1" outlineLevel="2">
       <c r="A280" s="38" t="n">
-        <v>68.5</v>
+        <v>69.5</v>
       </c>
       <c r="B280" s="19" t="n"/>
       <c r="C280" s="41" t="n"/>
@@ -5926,7 +5926,7 @@
     </row>
     <row r="281" hidden="1" outlineLevel="2">
       <c r="A281" s="38" t="n">
-        <v>68.75</v>
+        <v>69.75</v>
       </c>
       <c r="B281" s="19" t="n"/>
       <c r="C281" s="41" t="n"/>
@@ -5936,7 +5936,7 @@
     </row>
     <row r="282" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A282" s="38" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B282" s="19" t="n"/>
       <c r="C282" s="41" t="n"/>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="283" hidden="1" outlineLevel="2">
       <c r="A283" s="38" t="n">
-        <v>69.25</v>
+        <v>70.25</v>
       </c>
       <c r="B283" s="19" t="n"/>
       <c r="C283" s="41" t="n"/>
@@ -5956,7 +5956,7 @@
     </row>
     <row r="284" collapsed="1" ht="28.8" customHeight="1">
       <c r="A284" s="38" t="n">
-        <v>69.5</v>
+        <v>70.5</v>
       </c>
       <c r="B284" s="19" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
     </row>
     <row r="285" hidden="1" outlineLevel="2">
       <c r="A285" s="38" t="n">
-        <v>69.75</v>
+        <v>70.75</v>
       </c>
       <c r="B285" s="19" t="n"/>
       <c r="C285" s="41" t="n"/>
@@ -5990,7 +5990,7 @@
     </row>
     <row r="286" collapsed="1" ht="43.2" customHeight="1">
       <c r="A286" s="38" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B286" s="19" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
     </row>
     <row r="287" hidden="1" outlineLevel="2">
       <c r="A287" s="38" t="n">
-        <v>70.25</v>
+        <v>71.25</v>
       </c>
       <c r="B287" s="19" t="n"/>
       <c r="C287" s="41" t="n"/>
@@ -6024,7 +6024,7 @@
     </row>
     <row r="288" hidden="1" outlineLevel="2">
       <c r="A288" s="38" t="n">
-        <v>70.5</v>
+        <v>71.5</v>
       </c>
       <c r="B288" s="19" t="n"/>
       <c r="C288" s="41" t="n"/>
@@ -6034,7 +6034,7 @@
     </row>
     <row r="289" hidden="1" outlineLevel="2">
       <c r="A289" s="38" t="n">
-        <v>70.75</v>
+        <v>71.75</v>
       </c>
       <c r="B289" s="19" t="n"/>
       <c r="C289" s="41" t="n"/>
@@ -6044,7 +6044,7 @@
     </row>
     <row r="290" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A290" s="38" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B290" s="19" t="n"/>
       <c r="C290" s="41" t="n"/>
@@ -6054,7 +6054,7 @@
     </row>
     <row r="291" hidden="1" outlineLevel="2">
       <c r="A291" s="38" t="n">
-        <v>71.25</v>
+        <v>72.25</v>
       </c>
       <c r="B291" s="19" t="n"/>
       <c r="C291" s="41" t="n"/>
@@ -6064,7 +6064,7 @@
     </row>
     <row r="292" hidden="1" outlineLevel="2">
       <c r="A292" s="38" t="n">
-        <v>71.5</v>
+        <v>72.5</v>
       </c>
       <c r="B292" s="19" t="n"/>
       <c r="C292" s="41" t="n"/>
@@ -6074,7 +6074,7 @@
     </row>
     <row r="293" hidden="1" outlineLevel="2">
       <c r="A293" s="38" t="n">
-        <v>71.75</v>
+        <v>72.75</v>
       </c>
       <c r="B293" s="19" t="n"/>
       <c r="C293" s="41" t="n"/>
@@ -6084,7 +6084,7 @@
     </row>
     <row r="294" collapsed="1" ht="129.6" customHeight="1">
       <c r="A294" s="38" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B294" s="19" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
     </row>
     <row r="295" hidden="1" outlineLevel="2">
       <c r="A295" s="38" t="n">
-        <v>72.25</v>
+        <v>73.25</v>
       </c>
       <c r="B295" s="19" t="n"/>
       <c r="C295" s="41" t="n"/>
@@ -6119,7 +6119,7 @@
     </row>
     <row r="296" hidden="1" outlineLevel="2">
       <c r="A296" s="38" t="n">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
       <c r="B296" s="19" t="n"/>
       <c r="C296" s="41" t="n"/>
@@ -6129,7 +6129,7 @@
     </row>
     <row r="297" hidden="1" outlineLevel="2">
       <c r="A297" s="38" t="n">
-        <v>72.75</v>
+        <v>73.75</v>
       </c>
       <c r="B297" s="19" t="n"/>
       <c r="C297" s="41" t="n"/>
@@ -6139,7 +6139,7 @@
     </row>
     <row r="298" hidden="1" outlineLevel="1" collapsed="1">
       <c r="A298" s="38" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B298" s="19" t="n"/>
       <c r="C298" s="41" t="n"/>
@@ -6149,7 +6149,7 @@
     </row>
     <row r="299" hidden="1" outlineLevel="2">
       <c r="A299" s="38" t="n">
-        <v>73.25</v>
+        <v>74.25</v>
       </c>
       <c r="B299" s="19" t="n"/>
       <c r="C299" s="41" t="n"/>
@@ -6159,7 +6159,7 @@
     </row>
     <row r="300" hidden="1" outlineLevel="2">
       <c r="A300" s="38" t="n">
-        <v>73.5</v>
+        <v>74.5</v>
       </c>
       <c r="B300" s="19" t="n"/>
       <c r="C300" s="41" t="n"/>
@@ -6169,7 +6169,7 @@
     </row>
     <row r="301" hidden="1" outlineLevel="2">
       <c r="A301" s="38" t="n">
-        <v>73.75</v>
+        <v>74.75</v>
       </c>
       <c r="B301" s="19" t="n"/>
       <c r="C301" s="41" t="n"/>
@@ -6179,7 +6179,7 @@
     </row>
     <row r="302" collapsed="1" ht="57.6" customHeight="1">
       <c r="A302" s="38" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B302" s="19" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
     </row>
     <row r="303" hidden="1" outlineLevel="2">
       <c r="A303" s="38" t="n">
-        <v>74.25</v>
+        <v>75.25</v>
       </c>
       <c r="B303" s="19" t="n"/>
       <c r="C303" s="41" t="n"/>
@@ -6214,7 +6214,7 @@
     </row>
     <row r="304" hidden="1" outlineLevel="2">
       <c r="A304" s="38" t="n">
-        <v>74.5</v>
+        <v>75.5</v>
       </c>
       <c r="B304" s="19" t="n"/>
       <c r="C304" s="41" t="n"/>
@@ -6224,7 +6224,7 @@
     </row>
     <row r="305" hidden="1" outlineLevel="2">
       <c r="A305" s="38" t="n">
-        <v>74.75</v>
+        <v>75.75</v>
       </c>
       <c r="B305" s="19" t="n"/>
       <c r="C305" s="41" t="n"/>
@@ -6234,7 +6234,7 @@
     </row>
     <row r="306">
       <c r="A306" s="38" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B306" s="19" t="inlineStr">
         <is>
